--- a/salidas/empresas/CVS.xlsx
+++ b/salidas/empresas/CVS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38786506652832</v>
+        <v>18.38787078857422</v>
       </c>
       <c r="C3" t="n">
         <v>28.32999992370605</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>19.38742828369141</v>
+        <v>19.38742446899414</v>
       </c>
       <c r="C4" t="n">
         <v>29.8700008392334</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>19.3151798248291</v>
+        <v>19.31518173217773</v>
       </c>
       <c r="C5" t="n">
         <v>29.71999931335449</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.13235282897949</v>
+        <v>18.13235855102539</v>
       </c>
       <c r="C6" t="n">
         <v>27.89999961853027</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>19.95208549499512</v>
+        <v>19.95208740234375</v>
       </c>
       <c r="C7" t="n">
         <v>30.70000076293945</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>21.83144378662109</v>
+        <v>21.83144569396973</v>
       </c>
       <c r="C9" t="n">
         <v>33.54999923706055</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.90092849731445</v>
+        <v>20.90093231201172</v>
       </c>
       <c r="C10" t="n">
         <v>32.11999893188477</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.44502258300781</v>
+        <v>20.44501304626465</v>
       </c>
       <c r="C11" t="n">
         <v>31.3799991607666</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>18.74452209472656</v>
+        <v>18.74452590942383</v>
       </c>
       <c r="C12" t="n">
         <v>28.77000045776367</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.13879776000977</v>
+        <v>20.1387996673584</v>
       </c>
       <c r="C13" t="n">
         <v>30.90999984741211</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.95710563659668</v>
+        <v>21.95711326599121</v>
       </c>
       <c r="C14" t="n">
         <v>33.65000152587891</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>20.50200653076172</v>
+        <v>20.50200080871582</v>
       </c>
       <c r="C15" t="n">
         <v>31.42000007629395</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>22.27684783935547</v>
+        <v>22.2768497467041</v>
       </c>
       <c r="C16" t="n">
         <v>34.13999938964844</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>25.19119834899902</v>
+        <v>25.19119644165039</v>
       </c>
       <c r="C18" t="n">
         <v>38.54000091552734</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>23.82509422302246</v>
+        <v>23.82509803771973</v>
       </c>
       <c r="C19" t="n">
         <v>36.45000076293945</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>23.03981781005859</v>
+        <v>23.0398120880127</v>
       </c>
       <c r="C20" t="n">
         <v>35.18999862670898</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>24.7617359161377</v>
+        <v>24.76173782348633</v>
       </c>
       <c r="C21" t="n">
         <v>37.81999969482422</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.9467945098877</v>
+        <v>25.94679641723633</v>
       </c>
       <c r="C22" t="n">
         <v>39.63000106811523</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>27.31714820861816</v>
+        <v>27.31714057922363</v>
       </c>
       <c r="C23" t="n">
         <v>41.65999984741211</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>26.28767395019531</v>
+        <v>26.28767013549805</v>
       </c>
       <c r="C24" t="n">
         <v>40.09000015258789</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>25.55526542663574</v>
+        <v>25.55524635314941</v>
       </c>
       <c r="C26" t="n">
         <v>38.90999984741211</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>26.52072143554688</v>
+        <v>26.52072334289551</v>
       </c>
       <c r="C27" t="n">
         <v>40.38000106811523</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>26.6060905456543</v>
+        <v>26.60610198974609</v>
       </c>
       <c r="C28" t="n">
         <v>40.5099983215332</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>26.55383682250977</v>
+        <v>26.55383110046387</v>
       </c>
       <c r="C29" t="n">
         <v>40.36999893188477</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>28.1456241607666</v>
+        <v>28.14562034606934</v>
       </c>
       <c r="C30" t="n">
         <v>42.79000091552734</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>26.02762031555176</v>
+        <v>26.02763175964355</v>
       </c>
       <c r="C31" t="n">
         <v>39.56999969482422</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>24.11703109741211</v>
+        <v>24.11704254150391</v>
       </c>
       <c r="C33" t="n">
         <v>36.59999847412109</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>22.17977142333984</v>
+        <v>22.17976760864258</v>
       </c>
       <c r="C34" t="n">
         <v>33.65999984741211</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.24604415893555</v>
+        <v>20.24604988098145</v>
       </c>
       <c r="C35" t="n">
         <v>30.64999961853027</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.98438453674316</v>
+        <v>18.98438262939453</v>
       </c>
       <c r="C37" t="n">
         <v>28.73999977111816</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.80742835998535</v>
+        <v>17.80742645263672</v>
       </c>
       <c r="C38" t="n">
         <v>26.8799991607666</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>17.05220413208008</v>
+        <v>17.05220031738281</v>
       </c>
       <c r="C39" t="n">
         <v>25.73999977111816</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.1067943572998</v>
+        <v>21.10679244995117</v>
       </c>
       <c r="C41" t="n">
         <v>31.78000068664551</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>19.79177284240723</v>
+        <v>19.79177665710449</v>
       </c>
       <c r="C42" t="n">
         <v>29.79999923706055</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.16658210754395</v>
+        <v>21.16656684875488</v>
       </c>
       <c r="C43" t="n">
         <v>31.8700008392334</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.28728294372559</v>
+        <v>22.28728103637695</v>
       </c>
       <c r="C44" t="n">
         <v>33.47999954223633</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>20.6844367980957</v>
+        <v>20.68443870544434</v>
       </c>
       <c r="C48" t="n">
         <v>31.01000022888184</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>21.48486328125</v>
+        <v>21.4848690032959</v>
       </c>
       <c r="C49" t="n">
         <v>32.20999908447266</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>21.647705078125</v>
+        <v>21.64770317077637</v>
       </c>
       <c r="C50" t="n">
         <v>32.36999893188477</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.57058143615723</v>
+        <v>22.57058715820312</v>
       </c>
       <c r="C51" t="n">
         <v>33.75</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>24.44980812072754</v>
+        <v>24.44980239868164</v>
       </c>
       <c r="C52" t="n">
         <v>36.56000137329102</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>24.74910545349121</v>
+        <v>24.74909973144531</v>
       </c>
       <c r="C53" t="n">
         <v>36.91999816894531</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>23.21401214599609</v>
+        <v>23.21400833129883</v>
       </c>
       <c r="C54" t="n">
         <v>34.63000106811523</v>
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>20.63305854797363</v>
+        <v>20.63306045532227</v>
       </c>
       <c r="C56" t="n">
         <v>30.69000053405762</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>18.13880157470703</v>
+        <v>18.13880920410156</v>
       </c>
       <c r="C57" t="n">
         <v>26.97999954223633</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>21.1574592590332</v>
+        <v>21.1574535369873</v>
       </c>
       <c r="C58" t="n">
         <v>31.46999931335449</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.31509208679199</v>
+        <v>20.31508255004883</v>
       </c>
       <c r="C59" t="n">
         <v>30.1299991607666</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.90167999267578</v>
+        <v>20.90168571472168</v>
       </c>
       <c r="C60" t="n">
         <v>31</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>23.4435920715332</v>
+        <v>23.443603515625</v>
       </c>
       <c r="C61" t="n">
         <v>34.77000045776367</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>23.14159774780273</v>
+        <v>23.14159393310547</v>
       </c>
       <c r="C62" t="n">
         <v>34.20000076293945</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>22.37020874023438</v>
+        <v>22.37020111083984</v>
       </c>
       <c r="C63" t="n">
         <v>33.06000137329102</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>23.2227897644043</v>
+        <v>23.22279930114746</v>
       </c>
       <c r="C64" t="n">
         <v>34.31999969482422</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>24.59486961364746</v>
+        <v>24.59486770629883</v>
       </c>
       <c r="C65" t="n">
         <v>36.22000122070312</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>26.27209854125977</v>
+        <v>26.2720947265625</v>
       </c>
       <c r="C66" t="n">
         <v>38.68999862670898</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>25.51835823059082</v>
+        <v>25.51836585998535</v>
       </c>
       <c r="C67" t="n">
         <v>37.58000183105469</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>24.76654434204102</v>
+        <v>24.76654052734375</v>
       </c>
       <c r="C68" t="n">
         <v>36.34999847412109</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>24.46675682067871</v>
+        <v>24.46675491333008</v>
       </c>
       <c r="C69" t="n">
         <v>35.90999984741211</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.88605880737305</v>
+        <v>22.88605499267578</v>
       </c>
       <c r="C70" t="n">
         <v>33.59000015258789</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>24.84126281738281</v>
+        <v>24.84125709533691</v>
       </c>
       <c r="C71" t="n">
         <v>36.33000183105469</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>26.5575065612793</v>
+        <v>26.55751419067383</v>
       </c>
       <c r="C72" t="n">
         <v>38.84000015258789</v>
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>30.95497131347656</v>
+        <v>30.95496368408203</v>
       </c>
       <c r="C75" t="n">
         <v>45.09999847412109</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>30.74905586242676</v>
+        <v>30.74905204772949</v>
       </c>
       <c r="C76" t="n">
         <v>44.79999923706055</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>30.74042892456055</v>
+        <v>30.74042320251465</v>
       </c>
       <c r="C77" t="n">
         <v>44.61999893188477</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>30.96089172363281</v>
+        <v>30.96089744567871</v>
       </c>
       <c r="C78" t="n">
         <v>44.93999862670898</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>32.1941032409668</v>
+        <v>32.19408416748047</v>
       </c>
       <c r="C79" t="n">
         <v>46.72999954223633</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>31.27935028076172</v>
+        <v>31.27935600280762</v>
       </c>
       <c r="C80" t="n">
         <v>45.25</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>31.48671531677246</v>
+        <v>31.48671340942383</v>
       </c>
       <c r="C81" t="n">
         <v>45.54999923706055</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>33.47064208984375</v>
+        <v>33.47063064575195</v>
       </c>
       <c r="C82" t="n">
         <v>48.41999816894531</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>32.18676376342773</v>
+        <v>32.1867561340332</v>
       </c>
       <c r="C83" t="n">
         <v>46.40000152587891</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>32.26305770874023</v>
+        <v>32.2630615234375</v>
       </c>
       <c r="C84" t="n">
         <v>46.5099983215332</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>33.53943252563477</v>
+        <v>33.5394287109375</v>
       </c>
       <c r="C85" t="n">
         <v>48.34999847412109</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>35.67044448852539</v>
+        <v>35.67043685913086</v>
       </c>
       <c r="C86" t="n">
         <v>51.20000076293945</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>35.61470413208008</v>
+        <v>35.61469268798828</v>
       </c>
       <c r="C87" t="n">
         <v>51.11999893188477</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>38.3109016418457</v>
+        <v>38.31089782714844</v>
       </c>
       <c r="C88" t="n">
         <v>54.9900016784668</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>40.6943359375</v>
+        <v>40.69432830810547</v>
       </c>
       <c r="C89" t="n">
         <v>58.18000030517578</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>40.2746467590332</v>
+        <v>40.27463912963867</v>
       </c>
       <c r="C90" t="n">
         <v>57.58000183105469</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>39.99486541748047</v>
+        <v>39.994873046875</v>
       </c>
       <c r="C91" t="n">
         <v>57.18000030517578</v>
@@ -2590,7 +2602,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2619,7 +2631,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>39.84117126464844</v>
+        <v>39.84119033813477</v>
       </c>
       <c r="C94" t="n">
         <v>56.75</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>43.87633514404297</v>
+        <v>43.87633895874023</v>
       </c>
       <c r="C95" t="n">
         <v>62.2599983215332</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>47.18855285644531</v>
+        <v>47.18854522705078</v>
       </c>
       <c r="C96" t="n">
         <v>66.95999908447266</v>
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>47.91801452636719</v>
+        <v>47.91801071166992</v>
       </c>
       <c r="C98" t="n">
         <v>67.72000122070312</v>
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>52.97022247314453</v>
+        <v>52.97020721435547</v>
       </c>
       <c r="C100" t="n">
         <v>74.86000061035156</v>
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>55.62542724609375</v>
+        <v>55.62545776367188</v>
       </c>
       <c r="C102" t="n">
         <v>78.31999969482422</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>53.53025054931641</v>
+        <v>53.53026580810547</v>
       </c>
       <c r="C103" t="n">
         <v>75.37000274658203</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>54.42771530151367</v>
+        <v>54.42770004272461</v>
       </c>
       <c r="C104" t="n">
         <v>76.36000061035156</v>
@@ -2967,7 +2979,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>56.72995758056641</v>
+        <v>56.72996520996094</v>
       </c>
       <c r="C106" t="n">
         <v>79.58999633789062</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>61.36985015869141</v>
+        <v>61.36989212036133</v>
       </c>
       <c r="C107" t="n">
         <v>85.80999755859375</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.33912658691406</v>
+        <v>65.33914184570312</v>
       </c>
       <c r="C108" t="n">
         <v>91.36000061035156</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>68.87929534912109</v>
+        <v>68.87928771972656</v>
       </c>
       <c r="C109" t="n">
         <v>96.30999755859375</v>
@@ -3112,7 +3124,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>74.55032348632812</v>
+        <v>74.55034637451172</v>
       </c>
       <c r="C111" t="n">
         <v>103.870002746582</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>74.07662963867188</v>
+        <v>74.07664489746094</v>
       </c>
       <c r="C112" t="n">
         <v>103.2099990844727</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>71.50994110107422</v>
+        <v>71.50996398925781</v>
       </c>
       <c r="C113" t="n">
         <v>99.29000091552734</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>73.73538970947266</v>
+        <v>73.73539733886719</v>
       </c>
       <c r="C114" t="n">
         <v>102.379997253418</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>75.53591156005859</v>
+        <v>75.53591918945312</v>
       </c>
       <c r="C115" t="n">
         <v>104.879997253418</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>81.25862884521484</v>
+        <v>81.25862121582031</v>
       </c>
       <c r="C116" t="n">
         <v>112.4700012207031</v>
@@ -3315,7 +3327,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>69.70599365234375</v>
+        <v>69.70595550537109</v>
       </c>
       <c r="C118" t="n">
         <v>96.48000335693359</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>71.60985565185547</v>
+        <v>71.60984039306641</v>
       </c>
       <c r="C119" t="n">
         <v>98.77999877929688</v>
@@ -3402,7 +3414,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>70.87765502929688</v>
+        <v>70.87764739990234</v>
       </c>
       <c r="C121" t="n">
         <v>97.76999664306641</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>70.33670043945312</v>
+        <v>70.33669281005859</v>
       </c>
       <c r="C122" t="n">
         <v>96.58999633789062</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>70.75905609130859</v>
+        <v>70.75904083251953</v>
       </c>
       <c r="C123" t="n">
         <v>97.16999816894531</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>75.53604125976562</v>
+        <v>75.53603363037109</v>
       </c>
       <c r="C124" t="n">
         <v>103.7300033569336</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>73.48579406738281</v>
+        <v>73.48580932617188</v>
       </c>
       <c r="C125" t="n">
         <v>100.5</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>70.52445983886719</v>
+        <v>70.52445220947266</v>
       </c>
       <c r="C126" t="n">
         <v>96.44999694824219</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>70.00530242919922</v>
+        <v>70.00529479980469</v>
       </c>
       <c r="C127" t="n">
         <v>95.73999786376953</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>68.09581756591797</v>
+        <v>68.09580993652344</v>
       </c>
       <c r="C128" t="n">
         <v>92.72000122070312</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>68.59521484375</v>
+        <v>68.59523773193359</v>
       </c>
       <c r="C129" t="n">
         <v>93.40000152587891</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>65.35643768310547</v>
+        <v>65.35640716552734</v>
       </c>
       <c r="C130" t="n">
         <v>88.98999786376953</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>62.07040786743164</v>
+        <v>62.07041931152344</v>
       </c>
       <c r="C131" t="n">
         <v>84.09999847412109</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>56.7490348815918</v>
+        <v>56.7490234375</v>
       </c>
       <c r="C132" t="n">
         <v>76.88999938964844</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>58.23987197875977</v>
+        <v>58.23988342285156</v>
       </c>
       <c r="C133" t="n">
         <v>78.91000366210938</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>58.51778411865234</v>
+        <v>58.51774597167969</v>
       </c>
       <c r="C134" t="n">
         <v>78.80999755859375</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>59.83201217651367</v>
+        <v>59.8320198059082</v>
       </c>
       <c r="C135" t="n">
         <v>80.58000183105469</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>58.28759384155273</v>
+        <v>58.28756713867188</v>
       </c>
       <c r="C136" t="n">
         <v>78.5</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>61.60675048828125</v>
+        <v>61.60675811767578</v>
       </c>
       <c r="C137" t="n">
         <v>82.44000244140625</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>57.41447067260742</v>
+        <v>57.41445922851562</v>
       </c>
       <c r="C138" t="n">
         <v>76.83000183105469</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>60.12712478637695</v>
+        <v>60.12714004516602</v>
       </c>
       <c r="C139" t="n">
         <v>80.45999908447266</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>60.11948394775391</v>
+        <v>60.11947250366211</v>
       </c>
       <c r="C140" t="n">
         <v>79.93000030517578</v>
@@ -4011,7 +4023,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>61.16495513916016</v>
+        <v>61.16495132446289</v>
       </c>
       <c r="C142" t="n">
         <v>81.31999969482422</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.88409805297852</v>
+        <v>51.88410186767578</v>
       </c>
       <c r="C143" t="n">
         <v>68.52999877929688</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>57.99390411376953</v>
+        <v>57.99390029907227</v>
       </c>
       <c r="C144" t="n">
         <v>76.59999847412109</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>54.88979339599609</v>
+        <v>54.8897819519043</v>
       </c>
       <c r="C145" t="n">
         <v>72.5</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>59.94651794433594</v>
+        <v>59.94649887084961</v>
       </c>
       <c r="C146" t="n">
         <v>78.69000244140625</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>51.59712219238281</v>
+        <v>51.59711837768555</v>
       </c>
       <c r="C147" t="n">
         <v>67.73000335693359</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>47.39193725585938</v>
+        <v>47.39196014404297</v>
       </c>
       <c r="C148" t="n">
         <v>62.20999908447266</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.60386276245117</v>
+        <v>53.60386657714844</v>
       </c>
       <c r="C149" t="n">
         <v>69.83000183105469</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>48.6602897644043</v>
+        <v>48.66030502319336</v>
       </c>
       <c r="C150" t="n">
         <v>63.38999938964844</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>49.39723587036133</v>
+        <v>49.3972282409668</v>
       </c>
       <c r="C151" t="n">
         <v>64.34999847412109</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>50.16682434082031</v>
+        <v>50.16682815551758</v>
       </c>
       <c r="C152" t="n">
         <v>64.86000061035156</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>58.19538497924805</v>
+        <v>58.19537734985352</v>
       </c>
       <c r="C153" t="n">
         <v>75.23999786376953</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>60.88702774047852</v>
+        <v>60.88704299926758</v>
       </c>
       <c r="C154" t="n">
         <v>78.72000122070312</v>
@@ -4417,7 +4429,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>51.02759552001953</v>
+        <v>51.02758407592773</v>
       </c>
       <c r="C157" t="n">
         <v>65.51999664306641</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>51.44001007080078</v>
+        <v>51.44000625610352</v>
       </c>
       <c r="C158" t="n">
         <v>65.55000305175781</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>45.38177490234375</v>
+        <v>45.38178253173828</v>
       </c>
       <c r="C159" t="n">
         <v>57.83000183105469</v>
@@ -4560,11 +4572,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>42.32126998901367</v>
+        <v>42.3212776184082</v>
       </c>
       <c r="C160" t="n">
         <v>53.93000030517578</v>
@@ -4587,11 +4599,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>43.08370971679688</v>
+        <v>43.08370590209961</v>
       </c>
       <c r="C161" t="n">
         <v>54.38000106811523</v>
@@ -4614,11 +4626,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>41.49124526977539</v>
+        <v>41.49123764038086</v>
       </c>
       <c r="C162" t="n">
         <v>52.36999893188477</v>
@@ -4641,11 +4653,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>43.17086410522461</v>
+        <v>43.17086029052734</v>
       </c>
       <c r="C163" t="n">
         <v>54.4900016784668</v>
@@ -4668,7 +4680,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4695,7 +4707,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>50.41654205322266</v>
+        <v>50.41654586791992</v>
       </c>
       <c r="C166" t="n">
         <v>63.06999969482422</v>
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>53.47214508056641</v>
+        <v>53.47213745117188</v>
       </c>
       <c r="C167" t="n">
         <v>66.38999938964844</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>60.62430572509766</v>
+        <v>60.62432861328125</v>
       </c>
       <c r="C168" t="n">
         <v>75.26999664306641</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>59.83501052856445</v>
+        <v>59.83500289916992</v>
       </c>
       <c r="C169" t="n">
         <v>74.29000091552734</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.99252700805664</v>
+        <v>54.99253463745117</v>
       </c>
       <c r="C170" t="n">
         <v>67.81999969482422</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>47.98670196533203</v>
+        <v>47.98670959472656</v>
       </c>
       <c r="C171" t="n">
         <v>59.18000030517578</v>
@@ -4898,11 +4910,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>48.10832595825195</v>
+        <v>48.10832977294922</v>
       </c>
       <c r="C172" t="n">
         <v>59.33000183105469</v>
@@ -4927,7 +4939,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>53.61302185058594</v>
+        <v>53.61301422119141</v>
       </c>
       <c r="C174" t="n">
         <v>65.56999969482422</v>
@@ -4985,7 +4997,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>51.86453247070312</v>
+        <v>51.86452865600586</v>
       </c>
       <c r="C176" t="n">
         <v>62.93999862670898</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>51.1888313293457</v>
+        <v>51.18882751464844</v>
       </c>
       <c r="C177" t="n">
         <v>62.11999893188477</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>48.12344741821289</v>
+        <v>48.12342834472656</v>
       </c>
       <c r="C178" t="n">
         <v>58.40000152587891</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>46.61208724975586</v>
+        <v>46.61209106445312</v>
       </c>
       <c r="C179" t="n">
         <v>56.09000015258789</v>
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>56.33504867553711</v>
+        <v>56.33505249023438</v>
       </c>
       <c r="C180" t="n">
         <v>67.79000091552734</v>
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>56.75887298583984</v>
+        <v>56.75888061523438</v>
       </c>
       <c r="C181" t="n">
         <v>68.30000305175781</v>
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>59.94107818603516</v>
+        <v>59.94108963012695</v>
       </c>
       <c r="C182" t="n">
         <v>71.65000152587891</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>56.99631500244141</v>
+        <v>56.99631881713867</v>
       </c>
       <c r="C183" t="n">
         <v>68.12999725341797</v>
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>62.93606185913086</v>
+        <v>62.93603515625</v>
       </c>
       <c r="C184" t="n">
         <v>75.23000335693359</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>64.33423614501953</v>
+        <v>64.33421325683594</v>
       </c>
       <c r="C185" t="n">
         <v>76.40000152587891</v>
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>72.78864288330078</v>
+        <v>72.78862762451172</v>
       </c>
       <c r="C186" t="n">
         <v>86.44000244140625</v>
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>70.26240539550781</v>
+        <v>70.26242828369141</v>
       </c>
       <c r="C187" t="n">
         <v>83.44000244140625</v>
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>69.77298736572266</v>
+        <v>69.77300262451172</v>
       </c>
       <c r="C188" t="n">
         <v>82.36000061035156</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>73.18710327148438</v>
+        <v>73.18708801269531</v>
       </c>
       <c r="C189" t="n">
         <v>86.38999938964844</v>
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>71.89092254638672</v>
+        <v>71.89093017578125</v>
       </c>
       <c r="C190" t="n">
         <v>84.86000061035156</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>76.07490539550781</v>
+        <v>76.07489013671875</v>
       </c>
       <c r="C191" t="n">
         <v>89.27999877929688</v>
@@ -5478,7 +5490,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>87.90195465087891</v>
+        <v>87.90198516845703</v>
       </c>
       <c r="C193" t="n">
         <v>103.1600036621094</v>
@@ -5536,11 +5548,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>91.2415771484375</v>
+        <v>91.24156188964844</v>
       </c>
       <c r="C194" t="n">
         <v>106.5100021362305</v>
@@ -5565,11 +5577,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>88.79157257080078</v>
+        <v>88.79155731201172</v>
       </c>
       <c r="C195" t="n">
         <v>103.6500015258789</v>
@@ -5594,7 +5606,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5623,7 +5635,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>83.31036376953125</v>
+        <v>83.31034088134766</v>
       </c>
       <c r="C198" t="n">
         <v>96.75</v>
@@ -5681,11 +5693,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>79.78852081298828</v>
+        <v>79.78852844238281</v>
       </c>
       <c r="C199" t="n">
         <v>92.66000366210938</v>
@@ -5710,11 +5722,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>82.86799621582031</v>
+        <v>82.86800384521484</v>
       </c>
       <c r="C200" t="n">
         <v>95.68000030517578</v>
@@ -5739,11 +5751,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>85.00727081298828</v>
+        <v>85.00725555419922</v>
       </c>
       <c r="C201" t="n">
         <v>98.15000152587891</v>
@@ -5768,11 +5780,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>82.59951782226562</v>
+        <v>82.59950256347656</v>
       </c>
       <c r="C202" t="n">
         <v>95.37000274658203</v>
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>82.51435089111328</v>
+        <v>82.51434326171875</v>
       </c>
       <c r="C203" t="n">
         <v>94.69999694824219</v>
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>88.77044677734375</v>
+        <v>88.77045440673828</v>
       </c>
       <c r="C204" t="n">
         <v>101.879997253418</v>
@@ -5855,7 +5867,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>77.39907836914062</v>
+        <v>77.39909362792969</v>
       </c>
       <c r="C206" t="n">
         <v>88.22000122070312</v>
@@ -5913,11 +5925,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>73.29312133789062</v>
+        <v>73.29313659667969</v>
       </c>
       <c r="C207" t="n">
         <v>83.54000091552734</v>
@@ -5942,11 +5954,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>65.19527435302734</v>
+        <v>65.19526672363281</v>
       </c>
       <c r="C208" t="n">
         <v>74.30999755859375</v>
@@ -5971,11 +5983,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>64.84658050537109</v>
+        <v>64.84658813476562</v>
       </c>
       <c r="C209" t="n">
         <v>73.30999755859375</v>
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>60.17615509033203</v>
+        <v>60.17613983154297</v>
       </c>
       <c r="C210" t="n">
         <v>68.02999877929688</v>
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>61.14914703369141</v>
+        <v>61.14915466308594</v>
       </c>
       <c r="C211" t="n">
         <v>69.12999725341797</v>
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>66.60907745361328</v>
+        <v>66.60903930664062</v>
       </c>
       <c r="C212" t="n">
         <v>74.69000244140625</v>
@@ -6087,11 +6099,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>58.11905670166016</v>
+        <v>58.11904907226562</v>
       </c>
       <c r="C213" t="n">
         <v>65.16999816894531</v>
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>62.26595306396484</v>
+        <v>62.26594924926758</v>
       </c>
       <c r="C214" t="n">
         <v>69.81999969482422</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>62.07185363769531</v>
+        <v>62.07184982299805</v>
       </c>
       <c r="C215" t="n">
         <v>69.01000213623047</v>
@@ -6174,11 +6186,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>61.11840438842773</v>
+        <v>61.11841583251953</v>
       </c>
       <c r="C216" t="n">
         <v>67.94999694824219</v>
@@ -6203,7 +6215,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6232,11 +6244,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>67.50054168701172</v>
+        <v>67.50054931640625</v>
       </c>
       <c r="C218" t="n">
         <v>74.37000274658203</v>
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>67.50054168701172</v>
+        <v>67.50054931640625</v>
       </c>
       <c r="C219" t="n">
         <v>74.37000274658203</v>
@@ -6290,11 +6302,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>72.39268493652344</v>
+        <v>72.39266967773438</v>
       </c>
       <c r="C220" t="n">
         <v>79.76000213623047</v>
@@ -6319,11 +6331,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>62.05037689208984</v>
+        <v>62.05038070678711</v>
       </c>
       <c r="C221" t="n">
         <v>67.70999908447266</v>
@@ -6348,11 +6360,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>54.61826324462891</v>
+        <v>54.61825942993164</v>
       </c>
       <c r="C222" t="n">
         <v>59.59999847412109</v>
@@ -6377,11 +6389,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>54.1234016418457</v>
+        <v>54.12339782714844</v>
       </c>
       <c r="C223" t="n">
         <v>59.06000137329102</v>
@@ -6406,7 +6418,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6435,11 +6447,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>53.04771423339844</v>
+        <v>53.0477180480957</v>
       </c>
       <c r="C225" t="n">
         <v>57.2400016784668</v>
@@ -6464,7 +6476,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6493,7 +6505,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>56.08465957641602</v>
+        <v>56.08466339111328</v>
       </c>
       <c r="C228" t="n">
         <v>59.84999847412109</v>
@@ -6551,11 +6563,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>42.06583786010742</v>
+        <v>42.06584167480469</v>
       </c>
       <c r="C229" t="n">
         <v>44.88999938964844</v>
@@ -6580,11 +6592,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>53.59931945800781</v>
+        <v>53.59932327270508</v>
       </c>
       <c r="C230" t="n">
         <v>56.47999954223633</v>
@@ -6609,11 +6621,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>62.36805725097656</v>
+        <v>62.36804580688477</v>
       </c>
       <c r="C231" t="n">
         <v>65.72000122070312</v>
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>64.29451751708984</v>
+        <v>64.29450988769531</v>
       </c>
       <c r="C232" t="n">
         <v>67.75</v>
@@ -6667,11 +6679,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>63.960205078125</v>
+        <v>63.9602165222168</v>
       </c>
       <c r="C233" t="n">
         <v>66.70999908447266</v>
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>61.40026473999023</v>
+        <v>61.40027236938477</v>
       </c>
       <c r="C234" t="n">
         <v>64.04000091552734</v>
@@ -6725,7 +6737,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6754,11 +6766,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>60.18959045410156</v>
+        <v>60.1895866394043</v>
       </c>
       <c r="C236" t="n">
         <v>62.09999847412109</v>
@@ -6783,11 +6795,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>70.89965057373047</v>
+        <v>70.899658203125</v>
       </c>
       <c r="C237" t="n">
         <v>73.15000152587891</v>
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6841,7 +6853,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6870,7 +6882,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6957,11 +6969,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>78.71746826171875</v>
+        <v>78.71747589111328</v>
       </c>
       <c r="C243" t="n">
         <v>79.90000152587891</v>
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>85.86000061035156</v>
+        <v>85.05000305175781</v>
       </c>
       <c r="C250" t="n">
-        <v>85.86000061035156</v>
+        <v>85.05000305175781</v>
       </c>
       <c r="D250" t="n">
-        <v>114019900</v>
+        <v>121402000</v>
       </c>
       <c r="E250" t="n">
         <v>3.79</v>
       </c>
       <c r="F250" t="n">
-        <v>22.6543537230479</v>
+        <v>22.44063405059573</v>
       </c>
       <c r="G250" t="n">
         <v>1278970369</v>
       </c>
       <c r="H250" t="n">
-        <v>109812396662.9616</v>
+        <v>108776433786.5578</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0891497588713879</v>
+        <v>0.09492166741511117</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39537</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39627</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39628</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39718</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I7" t="n">
         <v>2.55</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K7" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I8" t="n">
         <v>2.6</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K8" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I9" t="n">
         <v>2.6</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K9" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I10" t="n">
         <v>2.48</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K10" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I11" t="n">
         <v>2.49</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K11" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I12" t="n">
         <v>2.46</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K12" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I13" t="n">
         <v>2.46</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K13" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I14" t="n">
         <v>2.52</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K14" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I15" t="n">
         <v>2.58</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="K15" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I16" t="n">
         <v>2.65</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K16" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I17" t="n">
         <v>2.8</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K17" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I18" t="n">
         <v>2.94</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K18" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I19" t="n">
         <v>3.03</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K19" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I20" t="n">
         <v>3.21</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K20" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I21" t="n">
         <v>3.37</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K21" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I22" t="n">
         <v>3.6</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K22" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41681</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I23" t="n">
         <v>3.75</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41681</v>
       </c>
       <c r="K23" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I24" t="n">
         <v>3.93</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K24" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I25" t="n">
         <v>4.08</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K25" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I26" t="n">
         <v>3.87</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K26" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42045</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I27" t="n">
         <v>3.96</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42045</v>
       </c>
       <c r="K27" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I28" t="n">
         <v>4.08</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K28" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I29" t="n">
         <v>4.140000000000001</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K29" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I30" t="n">
         <v>4.44</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K30" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I31" t="n">
         <v>4.640000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="K31" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I32" t="n">
         <v>4.61</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="K32" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I33" t="n">
         <v>4.35</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="K33" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I34" t="n">
         <v>4.67</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="K34" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I35" t="n">
         <v>4.92</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="K35" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I36" t="n">
         <v>4.8</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K36" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I37" t="n">
         <v>5.01</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="K37" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I38" t="n">
         <v>4.84</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="K38" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43145</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I39" t="n">
         <v>6.470000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43145</v>
       </c>
       <c r="K39" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I40" t="n">
         <v>6.530000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I41" t="n">
         <v>2.94</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="K41" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I42" t="n">
         <v>3.04</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K42" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I43" t="n">
         <v>-0.5499999999999997</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K43" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I44" t="n">
         <v>-0.4399999999999997</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K44" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I45" t="n">
         <v>3.57</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K45" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I46" t="n">
         <v>3.380000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K46" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I47" t="n">
         <v>5.08</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="K47" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I48" t="n">
         <v>5.52</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I49" t="n">
         <v>6.29</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K49" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I50" t="n">
         <v>6.05</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="K50" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I51" t="n">
         <v>5.46</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="K51" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I52" t="n">
         <v>5.61</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K52" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I53" t="n">
         <v>5.450000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K53" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I54" t="n">
         <v>5.720000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I55" t="n">
         <v>5.95</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="K55" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I56" t="n">
         <v>6.01</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I57" t="n">
         <v>6.140000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K57" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I58" t="n">
         <v>2.34</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I59" t="n">
         <v>3.140000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="K59" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I60" t="n">
         <v>3.050000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K60" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I61" t="n">
         <v>2.300000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K61" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I62" t="n">
         <v>6.65</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K62" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I63" t="n">
         <v>6.470000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="K63" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I64" t="n">
         <v>5.7</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I65" t="n">
         <v>5.630000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I66" t="n">
         <v>3.95</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="K66" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I67" t="n">
         <v>3.660000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K67" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I68" t="n">
         <v>4.190000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I69" t="n">
         <v>3.580000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I70" t="n">
         <v>0.3800000000000012</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="K70" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I71" t="n">
         <v>1.39</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="K71" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I72" t="n">
         <v>2.28</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10525,13 +10537,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I73" t="n">
         <v>3.79</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K73" t="n">
@@ -10595,52 +10607,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40024</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="C2" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40115</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40231</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40295</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C5" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40380</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="C6" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40477</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C7" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40585</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C8" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C11" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40949</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="C12" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41024</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C13" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C14" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41313</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="C16" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41388</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C17" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C19" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41674</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41681</v>
       </c>
       <c r="C20" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C21" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41942</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C23" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42038</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42045</v>
       </c>
       <c r="C24" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C25" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42214</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C27" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42403</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="C28" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42486</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="C29" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42577</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="C30" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="C31" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42769</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="C32" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42851</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C33" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="C34" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="C35" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43145</v>
       </c>
       <c r="C36" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43215</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C38" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C39" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43515</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C40" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43578</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43676</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C42" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43767</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C43" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43873</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="C44" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C45" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C46" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44132</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="C47" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44235</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="C48" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44313</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C49" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44405</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C50" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44496</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44594</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="C52" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44678</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44769</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C54" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44860</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="C56" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45042</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C57" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45224</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C59" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="C60" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45406</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C61" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C62" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45595</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C63" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45693</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C64" t="n">
@@ -12653,10 +12665,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45770</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C65" t="n">
@@ -12685,10 +12697,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C66" t="n">
@@ -12717,10 +12729,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45952</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C67" t="n">
@@ -12749,10 +12761,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46057</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="C68" t="n">
@@ -12781,10 +12793,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C69" t="n">
@@ -12813,10 +12825,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46232</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C70" t="n">
@@ -12863,12 +12875,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CVS.xlsx
+++ b/salidas/empresas/CVS.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>18.01790618896484</v>
+        <v>18.01790809631348</v>
       </c>
       <c r="C2" t="n">
         <v>27.76000022888184</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38787078857422</v>
+        <v>18.38786888122559</v>
       </c>
       <c r="C3" t="n">
         <v>28.32999992370605</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>19.38742446899414</v>
+        <v>19.38742065429688</v>
       </c>
       <c r="C4" t="n">
         <v>29.8700008392334</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>19.31518173217773</v>
+        <v>19.3151798248291</v>
       </c>
       <c r="C5" t="n">
         <v>29.71999931335449</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.13235855102539</v>
+        <v>18.13236236572266</v>
       </c>
       <c r="C6" t="n">
         <v>27.89999961853027</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>19.95208740234375</v>
+        <v>19.95208930969238</v>
       </c>
       <c r="C7" t="n">
         <v>30.70000076293945</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>21.29135894775391</v>
+        <v>21.29136085510254</v>
       </c>
       <c r="C8" t="n">
         <v>32.72000122070312</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>21.83144569396973</v>
+        <v>21.83144950866699</v>
       </c>
       <c r="C9" t="n">
         <v>33.54999923706055</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.90093231201172</v>
+        <v>20.90093612670898</v>
       </c>
       <c r="C10" t="n">
         <v>32.11999893188477</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>18.74452590942383</v>
+        <v>18.74452018737793</v>
       </c>
       <c r="C12" t="n">
         <v>28.77000045776367</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.1387996673584</v>
+        <v>20.13879203796387</v>
       </c>
       <c r="C13" t="n">
         <v>30.90999984741211</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.95711326599121</v>
+        <v>21.95711898803711</v>
       </c>
       <c r="C14" t="n">
         <v>33.65000152587891</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>20.50200080871582</v>
+        <v>20.50200271606445</v>
       </c>
       <c r="C15" t="n">
         <v>31.42000007629395</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>23.68783187866211</v>
+        <v>23.68783378601074</v>
       </c>
       <c r="C17" t="n">
         <v>36.2400016784668</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>25.19119644165039</v>
+        <v>25.19120597839355</v>
       </c>
       <c r="C18" t="n">
         <v>38.54000091552734</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>23.82509803771973</v>
+        <v>23.8250904083252</v>
       </c>
       <c r="C19" t="n">
         <v>36.45000076293945</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>23.0398120880127</v>
+        <v>23.03981018066406</v>
       </c>
       <c r="C20" t="n">
         <v>35.18999862670898</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>24.76173782348633</v>
+        <v>24.76173973083496</v>
       </c>
       <c r="C21" t="n">
         <v>37.81999969482422</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.94679641723633</v>
+        <v>25.94680404663086</v>
       </c>
       <c r="C22" t="n">
         <v>39.63000106811523</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>27.31714057922363</v>
+        <v>27.3171501159668</v>
       </c>
       <c r="C23" t="n">
         <v>41.65999984741211</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>26.06473350524902</v>
+        <v>26.06472206115723</v>
       </c>
       <c r="C25" t="n">
         <v>39.75</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>25.55524635314941</v>
+        <v>25.55525779724121</v>
       </c>
       <c r="C26" t="n">
         <v>38.90999984741211</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>26.52072334289551</v>
+        <v>26.52071762084961</v>
       </c>
       <c r="C27" t="n">
         <v>40.38000106811523</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>26.60610198974609</v>
+        <v>26.60609436035156</v>
       </c>
       <c r="C28" t="n">
         <v>40.5099983215332</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>26.55383110046387</v>
+        <v>26.5538272857666</v>
       </c>
       <c r="C29" t="n">
         <v>40.36999893188477</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>28.14562034606934</v>
+        <v>28.14561462402344</v>
       </c>
       <c r="C30" t="n">
         <v>42.79000091552734</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>26.02763175964355</v>
+        <v>26.02762222290039</v>
       </c>
       <c r="C31" t="n">
         <v>39.56999969482422</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>24.05113983154297</v>
+        <v>24.05114555358887</v>
       </c>
       <c r="C32" t="n">
         <v>36.5</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>22.17976760864258</v>
+        <v>22.17977523803711</v>
       </c>
       <c r="C34" t="n">
         <v>33.65999984741211</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.24604988098145</v>
+        <v>20.24605369567871</v>
       </c>
       <c r="C35" t="n">
         <v>30.64999961853027</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>19.10989379882812</v>
+        <v>19.10989952087402</v>
       </c>
       <c r="C36" t="n">
         <v>28.93000030517578</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.98438262939453</v>
+        <v>18.98439025878906</v>
       </c>
       <c r="C37" t="n">
         <v>28.73999977111816</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.80742645263672</v>
+        <v>17.80742073059082</v>
       </c>
       <c r="C38" t="n">
         <v>26.8799991607666</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>17.05220031738281</v>
+        <v>17.05220222473145</v>
       </c>
       <c r="C39" t="n">
         <v>25.73999977111816</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>18.2115421295166</v>
+        <v>18.21154403686523</v>
       </c>
       <c r="C40" t="n">
         <v>27.48999977111816</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.10679244995117</v>
+        <v>21.1067943572998</v>
       </c>
       <c r="C41" t="n">
         <v>31.78000068664551</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>19.79177665710449</v>
+        <v>19.79177284240723</v>
       </c>
       <c r="C42" t="n">
         <v>29.79999923706055</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.16656684875488</v>
+        <v>21.16657257080078</v>
       </c>
       <c r="C43" t="n">
         <v>31.8700008392334</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.28728103637695</v>
+        <v>22.28728294372559</v>
       </c>
       <c r="C44" t="n">
         <v>33.47999954223633</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.97666931152344</v>
+        <v>24.97665977478027</v>
       </c>
       <c r="C45" t="n">
         <v>37.52000045776367</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>23.79173851013184</v>
+        <v>23.79173278808594</v>
       </c>
       <c r="C46" t="n">
         <v>35.7400016784668</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>23.54597854614258</v>
+        <v>23.54597663879395</v>
       </c>
       <c r="C47" t="n">
         <v>35.29999923706055</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>20.68443870544434</v>
+        <v>20.68443489074707</v>
       </c>
       <c r="C48" t="n">
         <v>31.01000022888184</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>21.4848690032959</v>
+        <v>21.48486709594727</v>
       </c>
       <c r="C49" t="n">
         <v>32.20999908447266</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>21.64770317077637</v>
+        <v>21.647705078125</v>
       </c>
       <c r="C50" t="n">
         <v>32.36999893188477</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.57058715820312</v>
+        <v>22.57059097290039</v>
       </c>
       <c r="C51" t="n">
         <v>33.75</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>24.44980239868164</v>
+        <v>24.44979476928711</v>
       </c>
       <c r="C52" t="n">
         <v>36.56000137329102</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>24.74909973144531</v>
+        <v>24.74910354614258</v>
       </c>
       <c r="C53" t="n">
         <v>36.91999816894531</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>19.65448760986328</v>
+        <v>19.65448188781738</v>
       </c>
       <c r="C55" t="n">
         <v>29.31999969482422</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>20.63306045532227</v>
+        <v>20.63306427001953</v>
       </c>
       <c r="C56" t="n">
         <v>30.69000053405762</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>18.13880920410156</v>
+        <v>18.13880348205566</v>
       </c>
       <c r="C57" t="n">
         <v>26.97999954223633</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>21.1574535369873</v>
+        <v>21.15745544433594</v>
       </c>
       <c r="C58" t="n">
         <v>31.46999931335449</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.90168571472168</v>
+        <v>20.90168190002441</v>
       </c>
       <c r="C60" t="n">
         <v>31</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>23.443603515625</v>
+        <v>23.44359588623047</v>
       </c>
       <c r="C61" t="n">
         <v>34.77000045776367</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>23.14159393310547</v>
+        <v>23.14158821105957</v>
       </c>
       <c r="C62" t="n">
         <v>34.20000076293945</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>22.37020111083984</v>
+        <v>22.37020874023438</v>
       </c>
       <c r="C63" t="n">
         <v>33.06000137329102</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>23.22279930114746</v>
+        <v>23.22278785705566</v>
       </c>
       <c r="C64" t="n">
         <v>34.31999969482422</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>24.59486770629883</v>
+        <v>24.59486389160156</v>
       </c>
       <c r="C65" t="n">
         <v>36.22000122070312</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>26.2720947265625</v>
+        <v>26.27210426330566</v>
       </c>
       <c r="C66" t="n">
         <v>38.68999862670898</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>25.51836585998535</v>
+        <v>25.51836967468262</v>
       </c>
       <c r="C67" t="n">
         <v>37.58000183105469</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>24.76654052734375</v>
+        <v>24.76654624938965</v>
       </c>
       <c r="C68" t="n">
         <v>36.34999847412109</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>24.46675491333008</v>
+        <v>24.46675300598145</v>
       </c>
       <c r="C69" t="n">
         <v>35.90999984741211</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.88605499267578</v>
+        <v>22.88605308532715</v>
       </c>
       <c r="C70" t="n">
         <v>33.59000015258789</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>24.84125709533691</v>
+        <v>24.84126281738281</v>
       </c>
       <c r="C71" t="n">
         <v>36.33000183105469</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>26.55751419067383</v>
+        <v>26.55751037597656</v>
       </c>
       <c r="C72" t="n">
         <v>38.84000015258789</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>27.88401794433594</v>
+        <v>27.88402366638184</v>
       </c>
       <c r="C73" t="n">
         <v>40.77999877929688</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>28.6556453704834</v>
+        <v>28.65564346313477</v>
       </c>
       <c r="C74" t="n">
         <v>41.75</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>30.95496368408203</v>
+        <v>30.95497703552246</v>
       </c>
       <c r="C75" t="n">
         <v>45.09999847412109</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>30.74042320251465</v>
+        <v>30.74042892456055</v>
       </c>
       <c r="C77" t="n">
         <v>44.61999893188477</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>30.96089744567871</v>
+        <v>30.96089172363281</v>
       </c>
       <c r="C78" t="n">
         <v>44.93999862670898</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>31.27935600280762</v>
+        <v>31.27934265136719</v>
       </c>
       <c r="C80" t="n">
         <v>45.25</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>31.48671340942383</v>
+        <v>31.48673629760742</v>
       </c>
       <c r="C81" t="n">
         <v>45.54999923706055</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>33.47063064575195</v>
+        <v>33.47063827514648</v>
       </c>
       <c r="C82" t="n">
         <v>48.41999816894531</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>33.5394287109375</v>
+        <v>33.53943634033203</v>
       </c>
       <c r="C85" t="n">
         <v>48.34999847412109</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>35.67043685913086</v>
+        <v>35.67043304443359</v>
       </c>
       <c r="C86" t="n">
         <v>51.20000076293945</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>35.61469268798828</v>
+        <v>35.61471176147461</v>
       </c>
       <c r="C87" t="n">
         <v>51.11999893188477</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>38.31089782714844</v>
+        <v>38.31088256835938</v>
       </c>
       <c r="C88" t="n">
         <v>54.9900016784668</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>40.69432830810547</v>
+        <v>40.69433212280273</v>
       </c>
       <c r="C89" t="n">
         <v>58.18000030517578</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>40.27463912963867</v>
+        <v>40.27466201782227</v>
       </c>
       <c r="C90" t="n">
         <v>57.58000183105469</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>39.994873046875</v>
+        <v>39.99487686157227</v>
       </c>
       <c r="C91" t="n">
         <v>57.18000030517578</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>43.16888427734375</v>
+        <v>43.16889572143555</v>
       </c>
       <c r="C92" t="n">
         <v>61.4900016784668</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>40.75384140014648</v>
+        <v>40.75383377075195</v>
       </c>
       <c r="C93" t="n">
         <v>58.04999923706055</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>39.84119033813477</v>
+        <v>39.84118270874023</v>
       </c>
       <c r="C94" t="n">
         <v>56.75</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>43.87633895874023</v>
+        <v>43.87632369995117</v>
       </c>
       <c r="C95" t="n">
         <v>62.2599983215332</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>47.18854522705078</v>
+        <v>47.18855667114258</v>
       </c>
       <c r="C96" t="n">
         <v>66.95999908447266</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>50.43735504150391</v>
+        <v>50.4373664855957</v>
       </c>
       <c r="C97" t="n">
         <v>71.56999969482422</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>47.91801071166992</v>
+        <v>47.91802597045898</v>
       </c>
       <c r="C98" t="n">
         <v>67.72000122070312</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>51.75315093994141</v>
+        <v>51.75316619873047</v>
       </c>
       <c r="C99" t="n">
         <v>73.13999938964844</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>52.97020721435547</v>
+        <v>52.97021865844727</v>
       </c>
       <c r="C100" t="n">
         <v>74.86000061035156</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>51.64813232421875</v>
+        <v>51.64812850952148</v>
       </c>
       <c r="C101" t="n">
         <v>72.72000122070312</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>55.62545776367188</v>
+        <v>55.62546157836914</v>
       </c>
       <c r="C102" t="n">
         <v>78.31999969482422</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>53.53026580810547</v>
+        <v>53.5302619934082</v>
       </c>
       <c r="C103" t="n">
         <v>75.37000274658203</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>54.42770004272461</v>
+        <v>54.42770767211914</v>
       </c>
       <c r="C104" t="n">
         <v>76.36000061035156</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>56.63016891479492</v>
+        <v>56.63015365600586</v>
       </c>
       <c r="C105" t="n">
         <v>79.44999694824219</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>56.72996520996094</v>
+        <v>56.72997665405273</v>
       </c>
       <c r="C106" t="n">
         <v>79.58999633789062</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>61.36989212036133</v>
+        <v>61.36986541748047</v>
       </c>
       <c r="C107" t="n">
         <v>85.80999755859375</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>68.87928771972656</v>
+        <v>68.87930297851562</v>
       </c>
       <c r="C109" t="n">
         <v>96.30999755859375</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>74.55034637451172</v>
+        <v>74.55033111572266</v>
       </c>
       <c r="C111" t="n">
         <v>103.870002746582</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>74.07664489746094</v>
+        <v>74.07659912109375</v>
       </c>
       <c r="C112" t="n">
         <v>103.2099990844727</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>71.50996398925781</v>
+        <v>71.50994873046875</v>
       </c>
       <c r="C113" t="n">
         <v>99.29000091552734</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>73.73539733886719</v>
+        <v>73.73538970947266</v>
       </c>
       <c r="C114" t="n">
         <v>102.379997253418</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>75.53591918945312</v>
+        <v>75.53591156005859</v>
       </c>
       <c r="C115" t="n">
         <v>104.879997253418</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>81.25862121582031</v>
+        <v>81.25861358642578</v>
       </c>
       <c r="C116" t="n">
         <v>112.4700012207031</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>73.98310852050781</v>
+        <v>73.98313140869141</v>
       </c>
       <c r="C117" t="n">
         <v>102.4000015258789</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>69.70595550537109</v>
+        <v>69.70597076416016</v>
       </c>
       <c r="C118" t="n">
         <v>96.48000335693359</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>71.60984039306641</v>
+        <v>71.60983276367188</v>
       </c>
       <c r="C119" t="n">
         <v>98.77999877929688</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>68.20987701416016</v>
+        <v>68.20986938476562</v>
       </c>
       <c r="C120" t="n">
         <v>94.08999633789062</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>70.33669281005859</v>
+        <v>70.33667755126953</v>
       </c>
       <c r="C122" t="n">
         <v>96.58999633789062</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>70.75904083251953</v>
+        <v>70.75902557373047</v>
       </c>
       <c r="C123" t="n">
         <v>97.16999816894531</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>75.53603363037109</v>
+        <v>75.53602600097656</v>
       </c>
       <c r="C124" t="n">
         <v>103.7300033569336</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>73.48580932617188</v>
+        <v>73.48578643798828</v>
       </c>
       <c r="C125" t="n">
         <v>100.5</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>70.52445220947266</v>
+        <v>70.52443695068359</v>
       </c>
       <c r="C126" t="n">
         <v>96.44999694824219</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>70.00529479980469</v>
+        <v>70.00530242919922</v>
       </c>
       <c r="C127" t="n">
         <v>95.73999786376953</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>68.09580993652344</v>
+        <v>68.09583282470703</v>
       </c>
       <c r="C128" t="n">
         <v>92.72000122070312</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>68.59523773193359</v>
+        <v>68.59523010253906</v>
       </c>
       <c r="C129" t="n">
         <v>93.40000152587891</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>65.35640716552734</v>
+        <v>65.35642242431641</v>
       </c>
       <c r="C130" t="n">
         <v>88.98999786376953</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>62.07041931152344</v>
+        <v>62.07038879394531</v>
       </c>
       <c r="C131" t="n">
         <v>84.09999847412109</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>56.7490234375</v>
+        <v>56.74901580810547</v>
       </c>
       <c r="C132" t="n">
         <v>76.88999938964844</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>58.23988342285156</v>
+        <v>58.23989486694336</v>
       </c>
       <c r="C133" t="n">
         <v>78.91000366210938</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>58.51774597167969</v>
+        <v>58.51777648925781</v>
       </c>
       <c r="C134" t="n">
         <v>78.80999755859375</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>59.8320198059082</v>
+        <v>59.83202743530273</v>
       </c>
       <c r="C135" t="n">
         <v>80.58000183105469</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>58.28756713867188</v>
+        <v>58.28760147094727</v>
       </c>
       <c r="C136" t="n">
         <v>78.5</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>61.60675811767578</v>
+        <v>61.60676193237305</v>
       </c>
       <c r="C137" t="n">
         <v>82.44000244140625</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>57.41445922851562</v>
+        <v>57.41444396972656</v>
       </c>
       <c r="C138" t="n">
         <v>76.83000183105469</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>60.12714004516602</v>
+        <v>60.12713623046875</v>
       </c>
       <c r="C139" t="n">
         <v>80.45999908447266</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>60.11947250366211</v>
+        <v>60.11947631835938</v>
       </c>
       <c r="C140" t="n">
         <v>79.93000030517578</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>58.17140960693359</v>
+        <v>58.17139434814453</v>
       </c>
       <c r="C141" t="n">
         <v>77.33999633789062</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>61.16495132446289</v>
+        <v>61.16495513916016</v>
       </c>
       <c r="C142" t="n">
         <v>81.31999969482422</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.88410186767578</v>
+        <v>51.88411712646484</v>
       </c>
       <c r="C143" t="n">
         <v>68.52999877929688</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>57.99390029907227</v>
+        <v>57.993896484375</v>
       </c>
       <c r="C144" t="n">
         <v>76.59999847412109</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>59.94649887084961</v>
+        <v>59.94651794433594</v>
       </c>
       <c r="C146" t="n">
         <v>78.69000244140625</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>51.59711837768555</v>
+        <v>51.59712600708008</v>
       </c>
       <c r="C147" t="n">
         <v>67.73000335693359</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>47.39196014404297</v>
+        <v>47.39194869995117</v>
       </c>
       <c r="C148" t="n">
         <v>62.20999908447266</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.60386657714844</v>
+        <v>53.60386276245117</v>
       </c>
       <c r="C149" t="n">
         <v>69.83000183105469</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>48.66030502319336</v>
+        <v>48.6602897644043</v>
       </c>
       <c r="C150" t="n">
         <v>63.38999938964844</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>49.3972282409668</v>
+        <v>49.39722442626953</v>
       </c>
       <c r="C151" t="n">
         <v>64.34999847412109</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>50.16682815551758</v>
+        <v>50.16682434082031</v>
       </c>
       <c r="C152" t="n">
         <v>64.86000061035156</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>58.19537734985352</v>
+        <v>58.19537353515625</v>
       </c>
       <c r="C153" t="n">
         <v>75.23999786376953</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>56.37799835205078</v>
+        <v>56.37802124023438</v>
       </c>
       <c r="C155" t="n">
         <v>72.38999938964844</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>62.46051025390625</v>
+        <v>62.46050643920898</v>
       </c>
       <c r="C156" t="n">
         <v>80.19999694824219</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>51.02758407592773</v>
+        <v>51.027587890625</v>
       </c>
       <c r="C157" t="n">
         <v>65.51999664306641</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>45.38178253173828</v>
+        <v>45.38177490234375</v>
       </c>
       <c r="C159" t="n">
         <v>57.83000183105469</v>
@@ -4576,7 +4576,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>42.3212776184082</v>
+        <v>42.32126998901367</v>
       </c>
       <c r="C160" t="n">
         <v>53.93000030517578</v>
@@ -4603,7 +4603,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>43.08370590209961</v>
+        <v>43.08371734619141</v>
       </c>
       <c r="C161" t="n">
         <v>54.38000106811523</v>
@@ -4630,7 +4630,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>41.49123764038086</v>
+        <v>41.49124526977539</v>
       </c>
       <c r="C162" t="n">
         <v>52.36999893188477</v>
@@ -4657,7 +4657,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>43.17086029052734</v>
+        <v>43.17085647583008</v>
       </c>
       <c r="C163" t="n">
         <v>54.4900016784668</v>
@@ -4684,7 +4684,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>44.66103744506836</v>
+        <v>44.66104125976562</v>
       </c>
       <c r="C164" t="n">
         <v>55.86999893188477</v>
@@ -4711,7 +4711,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>48.69787979125977</v>
+        <v>48.6978874206543</v>
       </c>
       <c r="C165" t="n">
         <v>60.91999816894531</v>
@@ -4740,7 +4740,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>50.41654586791992</v>
+        <v>50.41653442382812</v>
       </c>
       <c r="C166" t="n">
         <v>63.06999969482422</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>53.47213745117188</v>
+        <v>53.47214508056641</v>
       </c>
       <c r="C167" t="n">
         <v>66.38999938964844</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>60.62432861328125</v>
+        <v>60.62430953979492</v>
       </c>
       <c r="C168" t="n">
         <v>75.26999664306641</v>
@@ -4827,7 +4827,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>59.83500289916992</v>
+        <v>59.83501434326172</v>
       </c>
       <c r="C169" t="n">
         <v>74.29000091552734</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.99253463745117</v>
+        <v>54.99252319335938</v>
       </c>
       <c r="C170" t="n">
         <v>67.81999969482422</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>47.98670959472656</v>
+        <v>47.98670196533203</v>
       </c>
       <c r="C171" t="n">
         <v>59.18000030517578</v>
@@ -4914,7 +4914,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>48.10832977294922</v>
+        <v>48.10833358764648</v>
       </c>
       <c r="C172" t="n">
         <v>59.33000183105469</v>
@@ -4972,7 +4972,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>53.61301422119141</v>
+        <v>53.61302185058594</v>
       </c>
       <c r="C174" t="n">
         <v>65.56999969482422</v>
@@ -5001,7 +5001,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>53.1224365234375</v>
+        <v>53.12243270874023</v>
       </c>
       <c r="C175" t="n">
         <v>64.97000122070312</v>
@@ -5030,7 +5030,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>51.86452865600586</v>
+        <v>51.86454010009766</v>
       </c>
       <c r="C176" t="n">
         <v>62.93999862670898</v>
@@ -5059,7 +5059,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>51.18882751464844</v>
+        <v>51.18883514404297</v>
       </c>
       <c r="C177" t="n">
         <v>62.11999893188477</v>
@@ -5088,7 +5088,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>48.12342834472656</v>
+        <v>48.12343215942383</v>
       </c>
       <c r="C178" t="n">
         <v>58.40000152587891</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>46.61209106445312</v>
+        <v>46.61207580566406</v>
       </c>
       <c r="C179" t="n">
         <v>56.09000015258789</v>
@@ -5175,7 +5175,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>56.75888061523438</v>
+        <v>56.75886535644531</v>
       </c>
       <c r="C181" t="n">
         <v>68.30000305175781</v>
@@ -5204,7 +5204,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>59.94108963012695</v>
+        <v>59.94107818603516</v>
       </c>
       <c r="C182" t="n">
         <v>71.65000152587891</v>
@@ -5233,7 +5233,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>56.99631881713867</v>
+        <v>56.99630355834961</v>
       </c>
       <c r="C183" t="n">
         <v>68.12999725341797</v>
@@ -5262,7 +5262,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>62.93603515625</v>
+        <v>62.9360466003418</v>
       </c>
       <c r="C184" t="n">
         <v>75.23000335693359</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>64.33421325683594</v>
+        <v>64.334228515625</v>
       </c>
       <c r="C185" t="n">
         <v>76.40000152587891</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>69.77300262451172</v>
+        <v>69.77299499511719</v>
       </c>
       <c r="C188" t="n">
         <v>82.36000061035156</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>73.18708801269531</v>
+        <v>73.18710327148438</v>
       </c>
       <c r="C189" t="n">
         <v>86.38999938964844</v>
@@ -5436,7 +5436,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>71.89093017578125</v>
+        <v>71.89090728759766</v>
       </c>
       <c r="C190" t="n">
         <v>84.86000061035156</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>75.88744354248047</v>
+        <v>75.88743591308594</v>
       </c>
       <c r="C192" t="n">
         <v>89.05999755859375</v>
@@ -5523,7 +5523,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>87.90198516845703</v>
+        <v>87.9019775390625</v>
       </c>
       <c r="C193" t="n">
         <v>103.1600036621094</v>
@@ -5552,7 +5552,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>91.24156188964844</v>
+        <v>91.2415771484375</v>
       </c>
       <c r="C194" t="n">
         <v>106.5100021362305</v>
@@ -5581,7 +5581,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>88.79155731201172</v>
+        <v>88.79156494140625</v>
       </c>
       <c r="C195" t="n">
         <v>103.6500015258789</v>
@@ -5610,7 +5610,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>86.70132446289062</v>
+        <v>86.70133209228516</v>
       </c>
       <c r="C196" t="n">
         <v>101.2099990844727</v>
@@ -5639,7 +5639,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>82.77648162841797</v>
+        <v>82.77647399902344</v>
       </c>
       <c r="C197" t="n">
         <v>96.12999725341797</v>
@@ -5668,7 +5668,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>83.31034088134766</v>
+        <v>83.31034851074219</v>
       </c>
       <c r="C198" t="n">
         <v>96.75</v>
@@ -5697,7 +5697,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>79.78852844238281</v>
+        <v>79.78849792480469</v>
       </c>
       <c r="C199" t="n">
         <v>92.66000366210938</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>85.00725555419922</v>
+        <v>85.00724029541016</v>
       </c>
       <c r="C201" t="n">
         <v>98.15000152587891</v>
@@ -5784,7 +5784,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>82.59950256347656</v>
+        <v>82.59951782226562</v>
       </c>
       <c r="C202" t="n">
         <v>95.37000274658203</v>
@@ -5813,7 +5813,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>82.51434326171875</v>
+        <v>82.51435089111328</v>
       </c>
       <c r="C203" t="n">
         <v>94.69999694824219</v>
@@ -5842,7 +5842,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>88.77045440673828</v>
+        <v>88.77044677734375</v>
       </c>
       <c r="C204" t="n">
         <v>101.879997253418</v>
@@ -5871,7 +5871,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>81.19865417480469</v>
+        <v>81.19863891601562</v>
       </c>
       <c r="C205" t="n">
         <v>93.19000244140625</v>
@@ -5900,7 +5900,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>77.39909362792969</v>
+        <v>77.39907073974609</v>
       </c>
       <c r="C206" t="n">
         <v>88.22000122070312</v>
@@ -5987,7 +5987,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>64.84658813476562</v>
+        <v>64.84657287597656</v>
       </c>
       <c r="C209" t="n">
         <v>73.30999755859375</v>
@@ -6016,7 +6016,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>60.17613983154297</v>
+        <v>60.1761474609375</v>
       </c>
       <c r="C210" t="n">
         <v>68.02999877929688</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>66.60903930664062</v>
+        <v>66.60906982421875</v>
       </c>
       <c r="C212" t="n">
         <v>74.69000244140625</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>58.11904907226562</v>
+        <v>58.11905288696289</v>
       </c>
       <c r="C213" t="n">
         <v>65.16999816894531</v>
@@ -6132,7 +6132,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>62.26594924926758</v>
+        <v>62.26594543457031</v>
       </c>
       <c r="C214" t="n">
         <v>69.81999969482422</v>
@@ -6190,7 +6190,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>61.11841583251953</v>
+        <v>61.118408203125</v>
       </c>
       <c r="C216" t="n">
         <v>67.94999694824219</v>
@@ -6219,7 +6219,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>71.021484375</v>
+        <v>71.02149200439453</v>
       </c>
       <c r="C217" t="n">
         <v>78.95999908447266</v>
@@ -6248,7 +6248,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>67.50054931640625</v>
+        <v>67.50054168701172</v>
       </c>
       <c r="C218" t="n">
         <v>74.37000274658203</v>
@@ -6277,7 +6277,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>67.50054931640625</v>
+        <v>67.50054168701172</v>
       </c>
       <c r="C219" t="n">
         <v>74.37000274658203</v>
@@ -6335,7 +6335,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>62.05038070678711</v>
+        <v>62.05037689208984</v>
       </c>
       <c r="C221" t="n">
         <v>67.70999908447266</v>
@@ -6364,7 +6364,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>54.61825942993164</v>
+        <v>54.61825561523438</v>
       </c>
       <c r="C222" t="n">
         <v>59.59999847412109</v>
@@ -6393,7 +6393,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>54.12339782714844</v>
+        <v>54.1234016418457</v>
       </c>
       <c r="C223" t="n">
         <v>59.06000137329102</v>
@@ -6422,7 +6422,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>55.91140365600586</v>
+        <v>55.91139602661133</v>
       </c>
       <c r="C224" t="n">
         <v>60.33000183105469</v>
@@ -6451,7 +6451,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>53.0477180480957</v>
+        <v>53.04771423339844</v>
       </c>
       <c r="C225" t="n">
         <v>57.2400016784668</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>58.27464294433594</v>
+        <v>58.27463531494141</v>
       </c>
       <c r="C226" t="n">
         <v>62.88000106811523</v>
@@ -6509,7 +6509,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>52.90793609619141</v>
+        <v>52.90793228149414</v>
       </c>
       <c r="C227" t="n">
         <v>56.45999908447266</v>
@@ -6538,7 +6538,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>56.08466339111328</v>
+        <v>56.08465957641602</v>
       </c>
       <c r="C228" t="n">
         <v>59.84999847412109</v>
@@ -6567,7 +6567,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>42.06584167480469</v>
+        <v>42.06583404541016</v>
       </c>
       <c r="C229" t="n">
         <v>44.88999938964844</v>
@@ -6596,7 +6596,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>53.59932327270508</v>
+        <v>53.59932708740234</v>
       </c>
       <c r="C230" t="n">
         <v>56.47999954223633</v>
@@ -6625,7 +6625,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>62.36804580688477</v>
+        <v>62.36805725097656</v>
       </c>
       <c r="C231" t="n">
         <v>65.72000122070312</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>63.9602165222168</v>
+        <v>63.96021270751953</v>
       </c>
       <c r="C233" t="n">
         <v>66.70999908447266</v>
@@ -6886,7 +6886,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>78.52458190917969</v>
+        <v>78.52458953857422</v>
       </c>
       <c r="C240" t="n">
         <v>80.36000061035156</v>
